--- a/Documentation/Best For Lists/Best for Loneliness List.xlsx
+++ b/Documentation/Best For Lists/Best for Loneliness List.xlsx
@@ -82,7 +82,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00999999"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -591,22 +591,22 @@
   <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -619,44 +619,44 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-27  |  Filter: one product per Manufacturer × Price Category × Animal Category  |  Tiebreaker: Score → Rating → Visual Contrast → Review Count  |  Products shown: 15  |  Eliminated: 14</t>
+          <t>Generated: 2026-07-02  |  Products shown: 15  |  Eliminated by dedup rule: 14</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Weights applied:</t>
+          <t>Weights:</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Autonomous interaction: 20%</t>
+          <t>autonomous interaction: 20%</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Emotional comfort potential: 30%</t>
+          <t>emotional comfort potential: 30%</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Realism level: 10%</t>
+          <t>realism level: 10%</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Sound quality: 10%</t>
+          <t>sound quality: 10%</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Tactile comfort: 15%</t>
+          <t>tactile comfort: 15%</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Touch responsiveness: 15%</t>
+          <t>touch responsiveness: 15%</t>
         </is>
       </c>
     </row>
@@ -684,8 +684,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Animal
-Type</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -756,27 +755,27 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Percy 1.1 Robotic Companion Dog</t>
+          <t>MateCat Pro</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Best Value</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="F5" s="8" t="n">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>5</v>
+        <v>456</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>4.4</v>
@@ -801,7 +800,7 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>Dog-form companion with touch sensors and heartbeat simulation. Weighted design for sensory relief per product documentation and buying-guide review (keyirobot.com). Feature set verified as broadly equivalent to MateCat Pro platform. Privacy=5: no camera or internet per Product Matrix. Product name updated to match repo: 'Percy 1.1 Robotic Companion Dog'. Review Strength=1: only 5 reviews at time of scoring (repo data, 2026-06-22).</t>
+          <t>Touch/voice verified via chongker.com product page and instruction manual (manuals.plus). Multi-zone sensors trigger purring/meowing/heartbeat/movement. Voice wake: responds to specific phrases. 180-day warranty per chongker.com. Sound Level Control=5: ON/MUTE/OFF + volume control. Privacy=5 confirmed: no camera, microphone, or WiFi per Product Matrix. Review Strength=3: 456 reviews, 4.6★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=5, Safety=5, Calmness=avg(Sound=4, Behavioral Realism=4)=4.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier C cap=4 -&gt; Final=4 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -816,30 +815,30 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>MateCat Pro</t>
+          <t>Percy 1.1 Robotic Companion Dog</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Best Value</t>
+          <t>Budget Friendly</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>456</v>
+        <v>5</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="J6" s="12" t="n">
         <v>3</v>
@@ -854,14 +853,14 @@
         <v>4</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O6" s="12" t="n">
         <v>5</v>
       </c>
       <c r="P6" s="11" t="inlineStr">
         <is>
-          <t>Touch/voice verified via chongker.com product page and instruction manual (manuals.plus). Multi-zone sensors trigger purring/meowing/heartbeat/movement. Voice wake: responds to specific phrases. 180-day warranty per chongker.com. Sound Level Control=5: ON/MUTE/OFF + volume control. Privacy=5 confirmed: no camera, microphone, or WiFi per Product Matrix. Review Strength=3: 456 reviews, 4.6★ (repo data, 2026-06-22).</t>
+          <t>Dog-form companion with touch sensors and heartbeat simulation. Weighted design for sensory relief per product documentation and buying-guide review (keyirobot.com). Feature set verified as broadly equivalent to MateCat Pro platform. Privacy=5: no camera or internet per Product Matrix. Product name updated to match repo: 'Percy 1.1 Robotic Companion Dog'. Review Strength=1: only 5 reviews at time of scoring (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 5 to 4. Percy line tier placed below MateCat (5) and above Joy for All (3) per Tim's tiering decision for the Chongker product family. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=5, Safety=5, Calmness=avg(Sound=4, Behavioral Realism=4)=4.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier C cap=4 -&gt; Final=4 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -899,7 +898,7 @@
         <v>16</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>3</v>
@@ -914,14 +913,14 @@
         <v>4</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>4</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>Cat-form Percy model. Assumed feature parity with Percy 1.1 Robotic Dog. Review strength=3: lower cumulative reviews than Percy 1.1. Verify current features against chongker.com Percy Robot Cat listing before publishing. Review Strength=2: 16 reviews, 5★ (repo data, 2026-06-22).</t>
+          <t>Cat-form Percy model. Assumed feature parity with Percy 1.1 Robotic Dog. Review strength=3: lower cumulative reviews than Percy 1.1. Verify current features against chongker.com Percy Robot Cat listing before publishing. Review Strength=2: 16 reviews, 5★ (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 5 to 4. Percy line tier placed below MateCat (5) and above Joy for All (3) per Tim's tiering decision for the Chongker product family. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=5, Safety=5, Calmness=avg(Sound=4, Behavioral Realism=4)=4.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier C cap=4 -&gt; Final=4 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -959,7 +958,7 @@
         <v>11640</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J8" s="12" t="n">
         <v>2</v>
@@ -974,14 +973,14 @@
         <v>3</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O8" s="12" t="n">
         <v>5</v>
       </c>
       <c r="P8" s="11" t="inlineStr">
         <is>
-          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Orange tabby coat — higher visual contrast against most furniture. Review Strength=5: 11,640 reviews, 4.5★ (repo data, 2026-06-22).</t>
+          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Orange tabby coat — higher visual contrast against most furniture. Review Strength=5: 11,640 reviews, 4.5★ (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 4 to 3. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier A — independent peer-reviewed research (Journal of Holistic Nursing, 2022). No cap; score reflects full 1-5 range. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=5, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier A cap=5 -&gt; Final=5 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1018,7 @@
         <v>5164</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>2</v>
@@ -1034,14 +1033,14 @@
         <v>3</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>5</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Review Strength=5: 5,164 reviews, 4.3★ (repo data, 2026-06-22).</t>
+          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Review Strength=5: 5,164 reviews, 4.3★ (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 4 to 3. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier A — independent peer-reviewed research (Journal of Holistic Nursing, 2022). No cap; score reflects full 1-5 range. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=5, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier A cap=5 -&gt; Final=5 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1100,7 @@
       </c>
       <c r="P10" s="11" t="inlineStr">
         <is>
-          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22).</t>
+          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=2, Safety=4, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=2.88, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1160,7 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>Detailed scoring performed in prior session against original product spec sheet. Review Strength: no verified current Amazon rating found — manual lookup required before publishing. Control accessibility=3: single ear-switch concealed in fur. Noise Sensitivity=5: explicit mute mode, designed to avoid motor noise per manufacturer. Amazon listing confirmed by Tim: https://www.amazon.com/Chongker-Breathing-Soothing-Interactive-Companion/dp/B0F83R6F75 — Amazon automated access blocked; star rating and review count require manual lookup before updating Review Strength score. Review Strength=1: only 2 reviews at time of scoring (repo data, 2026-06-22). Amazon URL confirmed: amazon.com/dp/B0F83R6F75 — automated fetch blocked; verify rating/count manually before next refresh Value for Money forced to 4 by Tim (June 2026) — consistent with other Chongker product family scores. See Product_Feature_Score_Details.xlsx for rationale.</t>
+          <t>Detailed scoring performed in prior session against original product spec sheet. Review Strength: no verified current Amazon rating found — manual lookup required before publishing. Control accessibility=3: single ear-switch concealed in fur. Noise Sensitivity=5: explicit mute mode, designed to avoid motor noise per manufacturer. Amazon listing confirmed by Tim: https://www.amazon.com/Chongker-Breathing-Soothing-Interactive-Companion/dp/B0F83R6F75 — Amazon automated access blocked; star rating and review count require manual lookup before updating Review Strength score. Review Strength=1: only 2 reviews at time of scoring (repo data, 2026-06-22). Amazon URL confirmed: amazon.com/dp/B0F83R6F75 — automated fetch blocked; verify rating/count manually before next refresh Value for Money forced to 4 by Tim (June 2026) — consistent with other Chongker product family scores. See Product_Feature_Score_Details.xlsx for rationale. TACTILE COMFORT REVIEW (2026-07-01): Considered for reclassification from MateCat tier (5) to Percy tier (4) alongside other Chongker Tactile Comfort changes. Manufacturer/Amazon listing describes cloud-like softness, silicone 'toe beans', and seamless ultra-soft faux fur construction with no competing hard internal mechanisms (no sensors/movement hardware, unlike Percy/MateCat robotic lines) — tactile comfort is the product's primary marketed feature. No independent (non-manufacturer) reviews found directly comparing its fur/feel against MateCat or Percy. Tim confirmed keeping this at 5 (MateCat tier) based on this evidence. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=3, Safety=4, Calmness=avg(Sound=4, Behavioral Realism=1)=2.5. Raw average of 4 sub-criteria=3.38, rounded=3, Evidence Tier C cap=4 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1220,7 @@
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>Hasbro 2023 'Hey Furby' — 25th anniversary edition. No app, no WiFi, no Bluetooth confirmed (Official Furby Wiki; IEEE Spectrum). 4x AA batteries. 5 voice-activated modes, 600+ pre-programmed reactions. Sound Level Control=2: no volume adjustment available (documented consumer complaint); only shutdown or mode switching. Brand=5: Hasbro, globally established, 58M+ units sold over 25 years. Review Strength=5: massive lifetime Amazon review volume. Dementia=2: loud/unpredictable, fantastical non-animal appearance — not recommended for memory care. Privacy=5: confirmed no wireless connectivity in 2023 model. IMPORTANT: DJ Furby (2025) is a different model from the Furby 2023 originally scored — elongated 'long oddbody' form factor with DJ/music theme (per Official Furby Wiki). Core feature scores carried over from 2023 Furby as closest available data; verify DJ-specific features (music modes, controls, form factor) before publishing. Review Strength=4: 772 reviews, 4.8★ (repo data, 2026-06-22). Visual contrast likely higher than regular Furby due to distinctive elongated DJ styling.</t>
+          <t>Hasbro 2023 'Hey Furby' — 25th anniversary edition. No app, no WiFi, no Bluetooth confirmed (Official Furby Wiki; IEEE Spectrum). 4x AA batteries. 5 voice-activated modes, 600+ pre-programmed reactions. Sound Level Control=2: no volume adjustment available (documented consumer complaint); only shutdown or mode switching. Brand=5: Hasbro, globally established, 58M+ units sold over 25 years. Review Strength=5: massive lifetime Amazon review volume. Dementia=2: loud/unpredictable, fantastical non-animal appearance — not recommended for memory care. Privacy=5: confirmed no wireless connectivity in 2023 model. IMPORTANT: DJ Furby (2025) is a different model from the Furby 2023 originally scored — elongated 'long oddbody' form factor with DJ/music theme (per Official Furby Wiki). Core feature scores carried over from 2023 Furby as closest available data; verify DJ-specific features (music modes, controls, form factor) before publishing. Review Strength=4: 772 reviews, 4.8★ (repo data, 2026-06-22). Visual contrast likely higher than regular Furby due to distinctive elongated DJ styling. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=3, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=3.75, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1280,7 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22).</t>
+          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1340,7 @@
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Quality=1 and Sound Level Control=1 — product produces no sounds; scores reflect absence of any sound output (lowest possible score on both scales). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY FLAG: With budget barking dogs=1 and Joy for All=3, Perfect Petzzz (no sounds at all) may need reconsideration — currently 1 pending Tim review.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1400,7 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Quality=1 and Sound Level Control=1 — product produces no sounds; scores reflect absence of any sound output (lowest possible score on both scales). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Beagle' per repo. Review Strength=3: 466 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY FLAG: With budget barking dogs=1 and Joy for All=3, Perfect Petzzz (no sounds at all) may need reconsideration — currently 1 pending Tim review.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Beagle' per repo. Review Strength=3: 466 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1460,7 @@
       </c>
       <c r="P16" s="11" t="inlineStr">
         <is>
-          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims.</t>
+          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=4, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=3.0, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1520,7 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22).</t>
+          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=3, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=2.75, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1580,7 @@
       </c>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22).</t>
+          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1641,15 +1640,15 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Product renamed in repo to 'EBO Air 2 FamilyBot'. Review Strength=3: 72 reviews, 4.5★ (repo data, 2026-06-22).</t>
+          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Product renamed in repo to 'EBO Air 2 FamilyBot'. Review Strength=3: 72 reviews, 4.5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:P1"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1677,7 +1676,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>Eliminated products — Best for Loneliness  (same Manufacturer × Price Category × Animal Category slot as a higher-scoring product)</t>
+          <t>Eliminated by dedup rule — Best for Loneliness  (same Manufacturer x Price Category x Animal Category as a higher-scoring product)</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1698,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -1745,7 +1744,7 @@
         </is>
       </c>
       <c r="E3" s="19" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="F3" s="19" t="n">
         <v>5</v>
@@ -1757,7 +1756,7 @@
       </c>
       <c r="H3" s="19" t="inlineStr">
         <is>
-          <t>Score=4.30 rating=5</t>
+          <t>score=4.15 rating=5</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1782,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="F4" s="20" t="n">
         <v>4.5</v>
@@ -1795,7 +1794,7 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>Score=3.85 rating=4.5</t>
+          <t>score=3.70 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1820,7 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="F5" s="19" t="n">
         <v>4.5</v>
@@ -1833,7 +1832,7 @@
       </c>
       <c r="H5" s="19" t="inlineStr">
         <is>
-          <t>Score=3.85 rating=4.5</t>
+          <t>score=3.70 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1858,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>4.3</v>
@@ -1871,7 +1870,7 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>Score=3.85 rating=4.3</t>
+          <t>score=3.70 rating=4.3</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1908,7 @@
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
-          <t>Score=3.65 rating=4</t>
+          <t>score=3.65 rating=4</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1946,7 @@
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>Score=2.70 rating=4.3</t>
+          <t>score=2.70 rating=4.3</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1984,7 @@
       </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
-          <t>Score=2.70 rating=4.1</t>
+          <t>score=2.70 rating=4.1</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2022,7 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>Score=2.70 rating=4</t>
+          <t>score=2.70 rating=4</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2060,7 @@
       </c>
       <c r="H11" s="19" t="inlineStr">
         <is>
-          <t>Score=2.70 rating=4.3</t>
+          <t>score=2.70 rating=4.3</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2098,7 @@
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>Score=2.70 rating=4.3</t>
+          <t>score=2.70 rating=4.3</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2136,7 @@
       </c>
       <c r="H13" s="19" t="inlineStr">
         <is>
-          <t>Score=2.70 rating=4.2</t>
+          <t>score=2.70 rating=4.2</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2174,7 @@
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>Score=1.75 rating=5</t>
+          <t>score=1.75 rating=5</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2212,7 @@
       </c>
       <c r="H15" s="19" t="inlineStr">
         <is>
-          <t>Score=1.75 rating=4.5</t>
+          <t>score=1.75 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2250,7 @@
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>Score=1.55 rating=5</t>
+          <t>score=1.55 rating=5</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2385,12 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>Whether sounds are soothing, realistic, or annoying. Absence of sound = 2 (neutral — not obnoxious, but not soothing either).</t>
+          <t>Whether sounds are soothing, realistic, or unsettling — including verified reports in retailer reviews (Amazon, Best Buy, Walmart) of a product startling users or being unsuitable for noise-sensitive/quiet environments. As of 2026-07, this feature absorbs the former 'Noise sensitivity fit' feature (eliminated as a separate row — overlapping scope). Products that produce no sound of any kind are scored N/A, not on the 1-5 scale.</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>1 – 5</t>
+          <t>1 - 5, or N/A if the product produces no sound of any kind</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2438,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
+    <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
           <t>TOTAL</t>

--- a/Documentation/Best For Lists/Best for Loneliness List.xlsx
+++ b/Documentation/Best For Lists/Best for Loneliness List.xlsx
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -619,7 +619,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-02  |  Products shown: 15  |  Eliminated by dedup rule: 14</t>
+          <t>Generated: 2026-07-07  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Original Black and White Shorthair Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1312,10 +1312,10 @@
         <v>44.45</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1200</v>
+        <v>848</v>
       </c>
       <c r="I14" s="16" t="n">
         <v>2.7</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Previously scored as 'Calico Cat' — now matched to 'Grey Tabby Cat' per repo. Verify this is the correct product match before publishing. Review Strength=4: 848 reviews, 4.3★ (repo data, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1372,10 +1372,10 @@
         <v>44.45</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>466</v>
+        <v>553</v>
       </c>
       <c r="I15" s="17" t="n">
         <v>2.7</v>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Beagle' per repo. Review Strength=3: 466 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Chocolate Lab' per repo. Review Strength=4: 553 reviews, 4.3★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1410,57 +1410,55 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Wuffy</t>
+          <t>Perfect Petzzz</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Wuffy Robot Puppy</t>
+          <t>Original Black and White Shorthair Cat</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Dog</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>25.99</v>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P16" s="11" t="inlineStr">
         <is>
-          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=4, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=3.0, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1468,12 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Ruko</t>
+          <t>Wuffy</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>18011 Smart Robot Dog</t>
+          <t>Wuffy Robot Puppy</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1489,22 +1487,22 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>69.98999999999999</v>
+        <v>25.99</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>2</v>
@@ -1513,14 +1511,14 @@
         <v>2</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>3</v>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=3, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=2.75, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=4, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=3.0, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1530,57 +1528,57 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Enabot</t>
+          <t>Ruko</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>EBO Air 2 Plus FamilyBot</t>
+          <t>18011 Smart Robot Dog</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Budget Friendly</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Robot</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>359</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>42</v>
+        <v>283</v>
       </c>
       <c r="I18" s="16" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=3, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=2.75, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1593,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>EBO Air 2 FamilyBot</t>
+          <t>EBO Air 2 Plus FamilyBot</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Best Value</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -1609,13 +1607,13 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>179</v>
+        <v>359</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="I19" s="17" t="n">
         <v>1.75</v>
@@ -1639,6 +1637,66 @@
         <v>2</v>
       </c>
       <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Enabot</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>EBO Air 2 FamilyBot</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Best Value</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Robot</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>179</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" s="11" t="inlineStr">
         <is>
           <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Product renamed in repo to 'EBO Air 2 FamilyBot'. Review Strength=3: 72 reviews, 4.5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
@@ -1660,7 +1718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1920,7 +1978,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Siamese Cat</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -1937,16 +1995,16 @@
         <v>2.7</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>Original Black and White Shorthair Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>score=2.70 rating=4.3</t>
+          <t>score=2.70 rating=4.1</t>
         </is>
       </c>
     </row>
@@ -1958,7 +2016,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Original Siamese Cat</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -1975,16 +2033,16 @@
         <v>2.7</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>Original Black and White Shorthair Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
-          <t>score=2.70 rating=4.1</t>
+          <t>score=2.70 rating=4</t>
         </is>
       </c>
     </row>
@@ -1996,24 +2054,24 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Original Plush White Cat</t>
+          <t>Original Beagle</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E10" s="20" t="n">
         <v>2.7</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
@@ -2022,7 +2080,7 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>score=2.70 rating=4</t>
+          <t>score=2.70 rating=0</t>
         </is>
       </c>
     </row>
@@ -2034,33 +2092,33 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Shih Tzu</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E11" s="19" t="n">
         <v>2.7</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>Original Black and White Shorthair Cat</t>
         </is>
       </c>
       <c r="H11" s="19" t="inlineStr">
         <is>
-          <t>score=2.70 rating=4.3</t>
+          <t>score=2.70 rating=0</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2151,7 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -2105,38 +2163,38 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>Perfect Petzzz</t>
+          <t>Enabot</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>Original Shih Tzu</t>
+          <t>EBO Air 2S FamilyBot</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Robot</t>
         </is>
       </c>
       <c r="E13" s="19" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>EBO Air 2 Plus FamilyBot</t>
         </is>
       </c>
       <c r="H13" s="19" t="inlineStr">
         <is>
-          <t>score=2.70 rating=4.2</t>
+          <t>score=1.75 rating=5</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2206,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>EBO Air 2S FamilyBot</t>
+          <t>EBO X FamilyBot</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -2165,7 +2223,7 @@
         <v>1.75</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
@@ -2174,7 +2232,7 @@
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>score=1.75 rating=5</t>
+          <t>score=1.75 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -2186,12 +2244,12 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>EBO X FamilyBot</t>
+          <t>ROLA Mini Pet Monitor</t>
         </is>
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Best Value</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -2200,55 +2258,17 @@
         </is>
       </c>
       <c r="E15" s="19" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
-          <t>EBO Air 2 Plus FamilyBot</t>
+          <t>EBO Air 2 FamilyBot</t>
         </is>
       </c>
       <c r="H15" s="19" t="inlineStr">
-        <is>
-          <t>score=1.75 rating=4.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Enabot</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>ROLA Mini Pet Monitor</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>Best Value</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>Robot</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="F16" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>EBO Air 2 FamilyBot</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>score=1.55 rating=5</t>
         </is>

--- a/Documentation/Best For Lists/Best for Loneliness List.xlsx
+++ b/Documentation/Best For Lists/Best for Loneliness List.xlsx
@@ -619,7 +619,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-07  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-08  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best for Loneliness List.xlsx
+++ b/Documentation/Best For Lists/Best for Loneliness List.xlsx
@@ -619,7 +619,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-08  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-11  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Robot</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
